--- a/artfynd/A 14981-2024 artfynd.xlsx
+++ b/artfynd/A 14981-2024 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117619467</v>
+        <v>117622152</v>
       </c>
       <c r="B3" t="n">
-        <v>78480</v>
+        <v>90499</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,34 +812,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Noret (Noret), Jmt</t>
+          <t>Norr-Nordtjärnen (Norr-Nordtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>484235</v>
+        <v>484170</v>
       </c>
       <c r="R3" t="n">
-        <v>6948756</v>
+        <v>6948819</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117622152</v>
+        <v>117619467</v>
       </c>
       <c r="B4" t="n">
-        <v>90499</v>
+        <v>78480</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,34 +924,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norr-Nordtjärnen (Norr-Nordtjärnen), Jmt</t>
+          <t>Noret (Noret), Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>484170</v>
+        <v>484235</v>
       </c>
       <c r="R4" t="n">
-        <v>6948819</v>
+        <v>6948756</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -983,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1137,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117617288</v>
+        <v>117618500</v>
       </c>
       <c r="B6" t="n">
-        <v>79561</v>
+        <v>57287</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,34 +1153,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Noret (Noret), Jmt</t>
+          <t>Nordtjärnarna, Berg (Nordtjärnarna, Berg), Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>484333</v>
+        <v>484294</v>
       </c>
       <c r="R6" t="n">
-        <v>6948798</v>
+        <v>6948791</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1212,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,10 +1254,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117618500</v>
+        <v>117617288</v>
       </c>
       <c r="B7" t="n">
-        <v>57287</v>
+        <v>79561</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,39 +1270,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nordtjärnarna, Berg (Nordtjärnarna, Berg), Jmt</t>
+          <t>Noret (Noret), Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>484294</v>
+        <v>484333</v>
       </c>
       <c r="R7" t="n">
-        <v>6948791</v>
+        <v>6948798</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 14981-2024 artfynd.xlsx
+++ b/artfynd/A 14981-2024 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117622152</v>
+        <v>117617458</v>
       </c>
       <c r="B3" t="n">
-        <v>90499</v>
+        <v>79597</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,38 +808,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norr-Nordtjärnen (Norr-Nordtjärnen), Jmt</t>
+          <t>Noret (Noret), Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>484170</v>
+        <v>484333</v>
       </c>
       <c r="R3" t="n">
-        <v>6948819</v>
+        <v>6948798</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117619467</v>
+        <v>117619216</v>
       </c>
       <c r="B4" t="n">
-        <v>78480</v>
+        <v>57287</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,34 +924,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Noret (Noret), Jmt</t>
+          <t>Nordtjärnarna, Berg (Nordtjärnarna, Berg), Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>484235</v>
+        <v>484250</v>
       </c>
       <c r="R4" t="n">
-        <v>6948756</v>
+        <v>6948725</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -983,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117618893</v>
+        <v>117623157</v>
       </c>
       <c r="B5" t="n">
-        <v>57287</v>
+        <v>90499</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,42 +1041,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nordtjärnarna, Berg (Nordtjärnarna, Berg), Jmt</t>
+          <t>Noret (Noret), Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>484261</v>
+        <v>484404</v>
       </c>
       <c r="R5" t="n">
-        <v>6948736</v>
+        <v>6948727</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1110,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>mycket rikligt med lågor av gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,7 +1142,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117618500</v>
+        <v>117618893</v>
       </c>
       <c r="B6" t="n">
         <v>57287</v>
@@ -1182,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>484294</v>
+        <v>484261</v>
       </c>
       <c r="R6" t="n">
-        <v>6948791</v>
+        <v>6948736</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1217,7 +1222,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1232,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,10 +1259,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117617288</v>
+        <v>117616618</v>
       </c>
       <c r="B7" t="n">
-        <v>79561</v>
+        <v>78480</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,21 +1275,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1294,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>484333</v>
+        <v>484308</v>
       </c>
       <c r="R7" t="n">
-        <v>6948798</v>
+        <v>6948768</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1329,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1339,7 +1344,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117616618</v>
+        <v>117617288</v>
       </c>
       <c r="B8" t="n">
-        <v>78480</v>
+        <v>79561</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,21 +1387,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1406,10 +1411,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>484308</v>
+        <v>484333</v>
       </c>
       <c r="R8" t="n">
-        <v>6948768</v>
+        <v>6948798</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1441,7 +1446,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1451,7 +1456,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1478,10 +1483,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117619216</v>
+        <v>117616123</v>
       </c>
       <c r="B9" t="n">
-        <v>57287</v>
+        <v>90499</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,39 +1499,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Nordtjärnarna, Berg (Nordtjärnarna, Berg), Jmt</t>
+          <t>Noret (Noret), Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>484250</v>
+        <v>484359</v>
       </c>
       <c r="R9" t="n">
-        <v>6948725</v>
+        <v>6948734</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1568,7 +1568,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt med död granved</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,10 +1600,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117617458</v>
+        <v>117615774</v>
       </c>
       <c r="B10" t="n">
-        <v>79597</v>
+        <v>57287</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,38 +1612,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Noret (Noret), Jmt</t>
+          <t>Nordtjärnarna, Berg (Nordtjärnarna, Berg), Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>484333</v>
+        <v>484351</v>
       </c>
       <c r="R10" t="n">
-        <v>6948798</v>
+        <v>6948721</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1670,7 +1680,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1680,7 +1690,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Grandominerad plats</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1707,10 +1722,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117617061</v>
+        <v>117615896</v>
       </c>
       <c r="B11" t="n">
-        <v>78480</v>
+        <v>97836</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,38 +1734,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Noret (Noret), Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>484359</v>
+        <v>484351</v>
       </c>
       <c r="R11" t="n">
-        <v>6948776</v>
+        <v>6948721</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1782,7 +1806,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1792,12 +1816,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:22</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1824,10 +1843,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117615774</v>
+        <v>117615250</v>
       </c>
       <c r="B12" t="n">
-        <v>57287</v>
+        <v>90499</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1840,39 +1859,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Nordtjärnarna, Berg (Nordtjärnarna, Berg), Jmt</t>
+          <t>Noret (Noret), Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>484351</v>
+        <v>484384</v>
       </c>
       <c r="R12" t="n">
-        <v>6948721</v>
+        <v>6948688</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1904,7 +1918,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1914,12 +1928,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:22</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Grandominerad plats</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1946,10 +1955,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117616123</v>
+        <v>117617061</v>
       </c>
       <c r="B13" t="n">
-        <v>90499</v>
+        <v>78480</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1962,21 +1971,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1989,7 +1998,7 @@
         <v>484359</v>
       </c>
       <c r="R13" t="n">
-        <v>6948734</v>
+        <v>6948776</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2021,7 +2030,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2031,12 +2040,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rikligt med död granved</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2063,7 +2072,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117615250</v>
+        <v>117622152</v>
       </c>
       <c r="B14" t="n">
         <v>90499</v>
@@ -2099,14 +2108,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Noret (Noret), Jmt</t>
+          <t>Norr-Nordtjärnen (Norr-Nordtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>484384</v>
+        <v>484170</v>
       </c>
       <c r="R14" t="n">
-        <v>6948688</v>
+        <v>6948819</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2138,7 +2147,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2148,7 +2157,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2175,10 +2184,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117615896</v>
+        <v>117619467</v>
       </c>
       <c r="B15" t="n">
-        <v>97836</v>
+        <v>78480</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2187,47 +2196,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Noret (Noret), Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>484351</v>
+        <v>484235</v>
       </c>
       <c r="R15" t="n">
-        <v>6948721</v>
+        <v>6948756</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2417,10 +2417,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117623157</v>
+        <v>117618500</v>
       </c>
       <c r="B17" t="n">
-        <v>90499</v>
+        <v>57287</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2433,37 +2433,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Noret (Noret), Jmt</t>
+          <t>Nordtjärnarna, Berg (Nordtjärnarna, Berg), Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>484404</v>
+        <v>484294</v>
       </c>
       <c r="R17" t="n">
-        <v>6948727</v>
+        <v>6948791</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2492,7 +2497,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2502,12 +2507,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>mycket rikligt med lågor av gran</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2534,10 +2534,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117635155</v>
+        <v>117635359</v>
       </c>
       <c r="B18" t="n">
-        <v>97836</v>
+        <v>90517</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2546,39 +2546,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2586,10 +2577,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>484174</v>
+        <v>484186</v>
       </c>
       <c r="R18" t="n">
-        <v>6948771</v>
+        <v>6948749</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2649,10 +2640,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117635359</v>
+        <v>117635155</v>
       </c>
       <c r="B19" t="n">
-        <v>90517</v>
+        <v>97836</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2661,30 +2652,39 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2692,10 +2692,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>484186</v>
+        <v>484174</v>
       </c>
       <c r="R19" t="n">
-        <v>6948749</v>
+        <v>6948771</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2861,10 +2861,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117662480</v>
+        <v>117662009</v>
       </c>
       <c r="B21" t="n">
-        <v>90495</v>
+        <v>57287</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2877,26 +2877,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2904,10 +2909,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>484228</v>
+        <v>484253</v>
       </c>
       <c r="R21" t="n">
-        <v>6948756</v>
+        <v>6948725</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2948,7 +2953,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2967,10 +2971,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117662009</v>
+        <v>117662480</v>
       </c>
       <c r="B22" t="n">
-        <v>57287</v>
+        <v>90495</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2983,31 +2987,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3015,10 +3014,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>484253</v>
+        <v>484228</v>
       </c>
       <c r="R22" t="n">
-        <v>6948725</v>
+        <v>6948756</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3059,6 +3058,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 14981-2024 artfynd.xlsx
+++ b/artfynd/A 14981-2024 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117617458</v>
+        <v>117623157</v>
       </c>
       <c r="B3" t="n">
-        <v>79597</v>
+        <v>90501</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,25 +808,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,13 +836,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>484333</v>
+        <v>484404</v>
       </c>
       <c r="R3" t="n">
-        <v>6948798</v>
+        <v>6948727</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>mycket rikligt med lågor av gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,7 +916,7 @@
         <v>117619216</v>
       </c>
       <c r="B4" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1025,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117623157</v>
+        <v>117622152</v>
       </c>
       <c r="B5" t="n">
-        <v>90499</v>
+        <v>90501</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1061,17 +1066,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Noret (Noret), Jmt</t>
+          <t>Norr-Nordtjärnen (Norr-Nordtjärnen), Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>484404</v>
+        <v>484170</v>
       </c>
       <c r="R5" t="n">
-        <v>6948727</v>
+        <v>6948819</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1100,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,12 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>mycket rikligt med lågor av gran</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117618893</v>
+        <v>117617061</v>
       </c>
       <c r="B6" t="n">
-        <v>57287</v>
+        <v>78482</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,39 +1158,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nordtjärnarna, Berg (Nordtjärnarna, Berg), Jmt</t>
+          <t>Noret (Noret), Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>484261</v>
+        <v>484359</v>
       </c>
       <c r="R6" t="n">
-        <v>6948736</v>
+        <v>6948776</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1222,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1232,7 +1227,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,10 +1259,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117616618</v>
+        <v>117617458</v>
       </c>
       <c r="B7" t="n">
-        <v>78480</v>
+        <v>79599</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,25 +1271,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>484308</v>
+        <v>484333</v>
       </c>
       <c r="R7" t="n">
-        <v>6948768</v>
+        <v>6948798</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117617288</v>
+        <v>117618893</v>
       </c>
       <c r="B8" t="n">
-        <v>79561</v>
+        <v>57288</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,34 +1387,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Noret (Noret), Jmt</t>
+          <t>Nordtjärnarna, Berg (Nordtjärnarna, Berg), Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>484333</v>
+        <v>484261</v>
       </c>
       <c r="R8" t="n">
-        <v>6948798</v>
+        <v>6948736</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1446,7 +1451,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1461,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1483,10 +1488,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117616123</v>
+        <v>117615774</v>
       </c>
       <c r="B9" t="n">
-        <v>90499</v>
+        <v>57288</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,34 +1504,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Noret (Noret), Jmt</t>
+          <t>Nordtjärnarna, Berg (Nordtjärnarna, Berg), Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>484359</v>
+        <v>484351</v>
       </c>
       <c r="R9" t="n">
-        <v>6948734</v>
+        <v>6948721</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1558,7 +1568,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1568,12 +1578,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rikligt med död granved</t>
+          <t>Grandominerad plats</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,10 +1610,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117615774</v>
+        <v>117615896</v>
       </c>
       <c r="B10" t="n">
-        <v>57287</v>
+        <v>97838</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1612,36 +1622,40 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nordtjärnarna, Berg (Nordtjärnarna, Berg), Jmt</t>
+          <t>Noret (Noret), Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
@@ -1680,7 +1694,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1690,12 +1704,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:22</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Grandominerad plats</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1722,10 +1731,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117615896</v>
+        <v>117617288</v>
       </c>
       <c r="B11" t="n">
-        <v>97836</v>
+        <v>79563</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1734,47 +1743,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Noret (Noret), Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>484351</v>
+        <v>484333</v>
       </c>
       <c r="R11" t="n">
-        <v>6948721</v>
+        <v>6948798</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1843,10 +1843,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117615250</v>
+        <v>117616123</v>
       </c>
       <c r="B12" t="n">
-        <v>90499</v>
+        <v>90501</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>484384</v>
+        <v>484359</v>
       </c>
       <c r="R12" t="n">
-        <v>6948688</v>
+        <v>6948734</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1928,7 +1928,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt med död granved</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1955,10 +1960,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117617061</v>
+        <v>117618500</v>
       </c>
       <c r="B13" t="n">
-        <v>78480</v>
+        <v>57288</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1971,34 +1976,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Noret (Noret), Jmt</t>
+          <t>Nordtjärnarna, Berg (Nordtjärnarna, Berg), Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>484359</v>
+        <v>484294</v>
       </c>
       <c r="R13" t="n">
-        <v>6948776</v>
+        <v>6948791</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2030,7 +2040,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2040,12 +2050,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:22</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2072,10 +2077,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117622152</v>
+        <v>117616618</v>
       </c>
       <c r="B14" t="n">
-        <v>90499</v>
+        <v>78482</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2088,34 +2093,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Norr-Nordtjärnen (Norr-Nordtjärnen), Jmt</t>
+          <t>Noret (Noret), Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>484170</v>
+        <v>484308</v>
       </c>
       <c r="R14" t="n">
-        <v>6948819</v>
+        <v>6948768</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2147,7 +2152,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2157,7 +2162,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2184,10 +2189,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117619467</v>
+        <v>117615250</v>
       </c>
       <c r="B15" t="n">
-        <v>78480</v>
+        <v>90501</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2200,21 +2205,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2224,10 +2229,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>484235</v>
+        <v>484384</v>
       </c>
       <c r="R15" t="n">
-        <v>6948756</v>
+        <v>6948688</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2259,7 +2264,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2269,7 +2274,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2296,10 +2301,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117615445</v>
+        <v>117619467</v>
       </c>
       <c r="B16" t="n">
-        <v>97836</v>
+        <v>78482</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2308,47 +2313,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Noret (Noret), Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>484384</v>
+        <v>484235</v>
       </c>
       <c r="R16" t="n">
-        <v>6948688</v>
+        <v>6948756</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2380,7 +2376,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2390,7 +2386,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2417,10 +2413,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117618500</v>
+        <v>117615445</v>
       </c>
       <c r="B17" t="n">
-        <v>57287</v>
+        <v>97838</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2429,43 +2425,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Nordtjärnarna, Berg (Nordtjärnarna, Berg), Jmt</t>
+          <t>Noret (Noret), Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>484294</v>
+        <v>484384</v>
       </c>
       <c r="R17" t="n">
-        <v>6948791</v>
+        <v>6948688</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2507,7 +2507,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2534,10 +2534,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117635359</v>
+        <v>117635155</v>
       </c>
       <c r="B18" t="n">
-        <v>90517</v>
+        <v>97838</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2546,30 +2546,39 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2577,10 +2586,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>484186</v>
+        <v>484174</v>
       </c>
       <c r="R18" t="n">
-        <v>6948749</v>
+        <v>6948771</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2640,10 +2649,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117635155</v>
+        <v>117635304</v>
       </c>
       <c r="B19" t="n">
-        <v>97836</v>
+        <v>90501</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2652,39 +2661,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2692,10 +2692,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>484174</v>
+        <v>484197</v>
       </c>
       <c r="R19" t="n">
-        <v>6948771</v>
+        <v>6948780</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2755,10 +2755,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117635304</v>
+        <v>117635359</v>
       </c>
       <c r="B20" t="n">
-        <v>90499</v>
+        <v>90519</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2771,21 +2771,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>484197</v>
+        <v>484186</v>
       </c>
       <c r="R20" t="n">
-        <v>6948780</v>
+        <v>6948749</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2864,7 +2864,7 @@
         <v>117662009</v>
       </c>
       <c r="B21" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>117662480</v>
       </c>
       <c r="B22" t="n">
-        <v>90495</v>
+        <v>90497</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 14981-2024 artfynd.xlsx
+++ b/artfynd/A 14981-2024 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117623157</v>
+        <v>117619216</v>
       </c>
       <c r="B3" t="n">
-        <v>90501</v>
+        <v>57288</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,37 +812,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Noret (Noret), Jmt</t>
+          <t>Nordtjärnarna, Berg (Nordtjärnarna, Berg), Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>484404</v>
+        <v>484250</v>
       </c>
       <c r="R3" t="n">
-        <v>6948727</v>
+        <v>6948725</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,12 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>mycket rikligt med lågor av gran</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117619216</v>
+        <v>117623157</v>
       </c>
       <c r="B4" t="n">
-        <v>57288</v>
+        <v>90501</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,42 +929,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nordtjärnarna, Berg (Nordtjärnarna, Berg), Jmt</t>
+          <t>Noret (Noret), Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>484250</v>
+        <v>484404</v>
       </c>
       <c r="R4" t="n">
-        <v>6948725</v>
+        <v>6948727</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +998,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>mycket rikligt med lågor av gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
